--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2233,6 +2233,612 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128620939</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92772</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>545321</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7009299</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128620941</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92935</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>545318</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7009221</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128620943</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90485</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>545381</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7009197</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128620940</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>545304</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7009264</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128620938</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80188</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>545387</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7009267</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128620942</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79083</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storbacken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>545383</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7009205</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92772</v>
+        <v>92778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>92935</v>
+        <v>92941</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90485</v>
+        <v>90491</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>128620940</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>128620938</v>
       </c>
       <c r="B19" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128620942</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92778</v>
+        <v>92784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>92941</v>
+        <v>92947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90491</v>
+        <v>90497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92784</v>
+        <v>92786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90497</v>
+        <v>90499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>128620940</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>128620938</v>
       </c>
       <c r="B19" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128620942</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92786</v>
+        <v>92787</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92787</v>
+        <v>92814</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>92950</v>
+        <v>92977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90499</v>
+        <v>90526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>128620940</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>128620938</v>
       </c>
       <c r="B19" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128620942</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92814</v>
+        <v>92819</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>92977</v>
+        <v>92982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>128620940</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>128620938</v>
       </c>
       <c r="B19" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128620942</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92819</v>
+        <v>92825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>92982</v>
+        <v>92989</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90531</v>
+        <v>90536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92825</v>
+        <v>92829</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>128620940</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>128620938</v>
       </c>
       <c r="B19" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128620942</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92829</v>
+        <v>92834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>128620940</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>128620938</v>
       </c>
       <c r="B19" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128620942</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92837</v>
+        <v>92842</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>93001</v>
+        <v>93006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90547</v>
+        <v>90552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>128620940</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>128620938</v>
       </c>
       <c r="B19" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128620942</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 31197-2023 artfynd.xlsx
+++ b/artfynd/A 31197-2023 artfynd.xlsx
@@ -2241,7 +2241,7 @@
         <v>128620939</v>
       </c>
       <c r="B15" t="n">
-        <v>92842</v>
+        <v>92850</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>128620941</v>
       </c>
       <c r="B16" t="n">
-        <v>93006</v>
+        <v>93014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>128620943</v>
       </c>
       <c r="B17" t="n">
-        <v>90552</v>
+        <v>90558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>128620940</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>128620938</v>
       </c>
       <c r="B19" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2746,7 +2746,7 @@
         <v>128620942</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
